--- a/Laporan_Forward_Testing_M15_PRO.xlsx
+++ b/Laporan_Forward_Testing_M15_PRO.xlsx
@@ -511,7 +511,7 @@
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -690,7 +690,7 @@
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="T3" s="9" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="T5" s="12" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="T6" s="9" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="T7" s="12" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" s="9" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T9" s="9" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="T10" s="12" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="T12" s="12" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="T13" s="9" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="T14" s="12" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="T17" s="9" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="T20" s="9" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal)</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="77" customWidth="1" min="2" max="2"/>
+    <col width="79" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>LightGBM PRO 57 Fitur (AI Adaptive Sniper) (28 Fitur SMC/ICT + DXY + MTF)</t>
+          <t>PRO V6 Dual-Engine (Hybrid Trend &amp; Reversal) (28 Fitur SMC/ICT + DXY + MTF)</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09 19:47:22 WIB</t>
+          <t>2026-10-10 01:46:19 WIB</t>
         </is>
       </c>
     </row>
